--- a/artfynd/A 33636-2025 artfynd.xlsx
+++ b/artfynd/A 33636-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1190,6 +1190,492 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128248669</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92653</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Marma gård, 450 m söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>666878</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6640739</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Ängsgranskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Mossbeväxt slutning</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128262224</v>
+      </c>
+      <c r="B7" t="n">
+        <v>95790</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gården vid Marma, 950 m söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>666959</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6640235</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Hassel, tall och gran intill bergbrant</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128248565</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92653</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Marma gård, 450 m söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>666863</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6640752</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Ängsgranskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Mossbeväxt sluttning</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128262355</v>
+      </c>
+      <c r="B9" t="n">
+        <v>95790</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gården vid Marma, 980 m söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>666968</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6640209</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Bergbrant med hassel skuggad av granskog</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33636-2025 artfynd.xlsx
+++ b/artfynd/A 33636-2025 artfynd.xlsx
@@ -1195,7 +1195,7 @@
         <v>128248669</v>
       </c>
       <c r="B6" t="n">
-        <v>92653</v>
+        <v>92654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>128248565</v>
       </c>
       <c r="B8" t="n">
-        <v>92653</v>
+        <v>92654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 33636-2025 artfynd.xlsx
+++ b/artfynd/A 33636-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1676,6 +1676,127 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128296941</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97160</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2609</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsfliksmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lejeunea cavifolia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ehrh.) Lindb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gården vid Marma, 800 m söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>666945</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6640384</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stone/rock on land # Stort flyttblock</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33636-2025 artfynd.xlsx
+++ b/artfynd/A 33636-2025 artfynd.xlsx
@@ -1195,7 +1195,7 @@
         <v>128248669</v>
       </c>
       <c r="B6" t="n">
-        <v>92654</v>
+        <v>92662</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128262224</v>
       </c>
       <c r="B7" t="n">
-        <v>95790</v>
+        <v>95798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>128248565</v>
       </c>
       <c r="B8" t="n">
-        <v>92654</v>
+        <v>92662</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128262355</v>
       </c>
       <c r="B9" t="n">
-        <v>95790</v>
+        <v>95798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>128296941</v>
       </c>
       <c r="B10" t="n">
-        <v>97160</v>
+        <v>97168</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33636-2025 artfynd.xlsx
+++ b/artfynd/A 33636-2025 artfynd.xlsx
@@ -1195,7 +1195,7 @@
         <v>128248669</v>
       </c>
       <c r="B6" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128262224</v>
       </c>
       <c r="B7" t="n">
-        <v>95798</v>
+        <v>95891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>128248565</v>
       </c>
       <c r="B8" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128262355</v>
       </c>
       <c r="B9" t="n">
-        <v>95798</v>
+        <v>95891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>128296941</v>
       </c>
       <c r="B10" t="n">
-        <v>97168</v>
+        <v>97261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33636-2025 artfynd.xlsx
+++ b/artfynd/A 33636-2025 artfynd.xlsx
@@ -1195,7 +1195,7 @@
         <v>128248669</v>
       </c>
       <c r="B6" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128262224</v>
       </c>
       <c r="B7" t="n">
-        <v>95891</v>
+        <v>95903</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>128248565</v>
       </c>
       <c r="B8" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128262355</v>
       </c>
       <c r="B9" t="n">
-        <v>95891</v>
+        <v>95903</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>128296941</v>
       </c>
       <c r="B10" t="n">
-        <v>97261</v>
+        <v>97273</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33636-2025 artfynd.xlsx
+++ b/artfynd/A 33636-2025 artfynd.xlsx
@@ -1195,7 +1195,7 @@
         <v>128248669</v>
       </c>
       <c r="B6" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128262224</v>
       </c>
       <c r="B7" t="n">
-        <v>95903</v>
+        <v>95905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>128248565</v>
       </c>
       <c r="B8" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128262355</v>
       </c>
       <c r="B9" t="n">
-        <v>95903</v>
+        <v>95905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>128296941</v>
       </c>
       <c r="B10" t="n">
-        <v>97273</v>
+        <v>97275</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33636-2025 artfynd.xlsx
+++ b/artfynd/A 33636-2025 artfynd.xlsx
@@ -1195,7 +1195,7 @@
         <v>128248669</v>
       </c>
       <c r="B6" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128262224</v>
       </c>
       <c r="B7" t="n">
-        <v>95905</v>
+        <v>95906</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>128248565</v>
       </c>
       <c r="B8" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128262355</v>
       </c>
       <c r="B9" t="n">
-        <v>95905</v>
+        <v>95906</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>128296941</v>
       </c>
       <c r="B10" t="n">
-        <v>97275</v>
+        <v>97276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33636-2025 artfynd.xlsx
+++ b/artfynd/A 33636-2025 artfynd.xlsx
@@ -1195,7 +1195,7 @@
         <v>128248669</v>
       </c>
       <c r="B6" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128262224</v>
       </c>
       <c r="B7" t="n">
-        <v>95906</v>
+        <v>95933</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>128248565</v>
       </c>
       <c r="B8" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128262355</v>
       </c>
       <c r="B9" t="n">
-        <v>95906</v>
+        <v>95933</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>128296941</v>
       </c>
       <c r="B10" t="n">
-        <v>97276</v>
+        <v>97303</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33636-2025 artfynd.xlsx
+++ b/artfynd/A 33636-2025 artfynd.xlsx
@@ -1195,7 +1195,7 @@
         <v>128248669</v>
       </c>
       <c r="B6" t="n">
-        <v>92796</v>
+        <v>92806</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128262224</v>
       </c>
       <c r="B7" t="n">
-        <v>95933</v>
+        <v>95946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>128248565</v>
       </c>
       <c r="B8" t="n">
-        <v>92796</v>
+        <v>92806</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128262355</v>
       </c>
       <c r="B9" t="n">
-        <v>95933</v>
+        <v>95946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>128296941</v>
       </c>
       <c r="B10" t="n">
-        <v>97303</v>
+        <v>97316</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
